--- a/reference/input/reference.xlsx
+++ b/reference/input/reference.xlsx
@@ -2041,12 +2041,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>The image's source.</t>
+          <t>The source of the element's media: an image in `&lt;picture&gt;`, `&lt;frame&gt;` and `&lt;cover&gt;`, or an audio clip in `&lt;audio&gt;`.</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Can only be part of the picture-specific element body sequence of `&lt;picture&gt;`.</t>
+          <t>Can only be part of the picture-specific element body sequence of `&lt;picture&gt;`, or come right after the element head of `&lt;frame&gt;`, `&lt;cover&gt;` or `&lt;audio&gt;`.</t>
         </is>
       </c>
       <c r="E38" s="6" t="b">

--- a/reference/input/reference.xlsx
+++ b/reference/input/reference.xlsx
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Captures a code snippet, either as a standalone block or inlined within a semantic element. For language classification, use a `&lt;label&gt;`in the element head (see [Recommendations](#recommendations)).</t>
+          <t>Captures a code snippet, either as a standalone block or inlined within a semantic element. For language classification, use a `&lt;label&gt;`in the element head (see [Recommendations](#annex-c-informative-recommendations)).</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Optional part of the element head; custom metadata, e.g. for application-specific purposes. See [Recommendations](#recommendations) for naming and namespacing guidance for custom vocabularies.</t>
+          <t>Optional part of the element head; custom metadata, e.g. for application-specific purposes. See [Recommendations](#annex-c-informative-recommendations) for naming and namespacing guidance for custom vocabularies.</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">

--- a/reference/input/reference.xlsx
+++ b/reference/input/reference.xlsx
@@ -4057,17 +4057,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Optional; default: "0.7"</t>
+          <t>Optional; if omitted, the version is unspecified</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{"0.7"}</t>
+          <t>"MAJOR.MINOR" of a published DocLang specification version</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The DocLang specification version the DocLang instance is supposed to validate against, in "MAJOR.MINOR" format, i.e. first two positions of Semantic Verisoning.</t>
+          <t>The DocLang specification version the DocLang instance is supposed to validate against, in "MAJOR.MINOR" format, i.e. first two positions of Semantic Versioning. If omitted, the version is unspecified (see [Omitted version](#omitted-version)).</t>
         </is>
       </c>
     </row>

--- a/reference/input/reference.xlsx
+++ b/reference/input/reference.xlsx
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Indicates the beginning of a corner cell, typically the top-left header intersection.</t>
+          <t>Indicates the beginning of a corner cell, typically where the column headers and the row headers meet.</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Left-merge extension token; extends the previous cell horizontally (colspan continuation).</t>
+          <t>Left-merge extension token; extends the previous cell in the same row (colspan continuation).</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Upward-merge extension token; extends the cell above vertically (rowspan continuation)</t>
+          <t>Upward-merge extension token; extends the cell at the same position in the previous row (rowspan continuation).</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Cross/combined span extension token; used where both horizontal and vertical spanning intersect.</t>
+          <t>Cross/combined span extension token; used where a colspan continuation and a rowspan continuation intersect.</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">

--- a/reference/input/reference.xlsx
+++ b/reference/input/reference.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="20" defaultRowHeight="16"/>
   <cols>
     <col width="27.1640625" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -3967,6 +3967,43 @@
         <v>0</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>[03a] property (outer)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>`&lt;writing_mode&gt;`</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Optional part of the element head, or of the document head; declares the writing mode, i.e. whether lines are horizontal or vertical, and the direction in which lines follow each other. In `&lt;head&gt;`, it sets the default writing mode of the DocLang instance. In an element head, it sets the writing mode of the host element and of its descendants. An element without `&lt;writing_mode&gt;` takes the writing mode of its nearest ancestor that declares one, otherwise the default of the DocLang instance, otherwise "horizontal_tb". The writing mode does not change the order of the content, which is always the reading order, nor the coordinate system of `&lt;location&gt;`.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Can only be part of the [element head](#element-head) of a semantic element, or child of `&lt;head&gt;`.</t>
+        </is>
+      </c>
+      <c r="E89" t="b">
+        <v>0</v>
+      </c>
+      <c r="F89" t="b">
+        <v>0</v>
+      </c>
+      <c r="G89" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" t="b">
+        <v>0</v>
+      </c>
+      <c r="I89" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H82"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3980,7 +4017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col width="12.5" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4633,6 +4670,33 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>`&lt;writing_mode&gt;`</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>`value`</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{"horizontal_tb", "vertical_rl", "vertical_lr"}</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>The writing mode: "horizontal_tb" for horizontal lines that follow each other from top to bottom; "vertical_rl" for vertical lines, read from top to bottom, that follow each other from right to left (e.g. traditional Japanese or Chinese); "vertical_lr" for vertical lines, read from top to bottom, that follow each other from left to right (e.g. traditional Mongolian). The values correspond to the CSS `writing-mode` values "horizontal-tb", "vertical-rl" and "vertical-lr" (see Bibliography [4]).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
